--- a/Tracker_Overview.xlsx
+++ b/Tracker_Overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SmartData\repos\AcesstoServices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C115F46C-B859-41EF-9E74-9AF15A017708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22322ACD-499C-49B4-A3B3-219C17708534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="167">
   <si>
     <t>Country</t>
   </si>
@@ -523,6 +523,30 @@
 Peruskoulut
 Peruskouluasteen erityiskoulut
 Perus- ja lukioasteen koulut</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> f</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>ε</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
   </si>
 </sst>
 </file>
@@ -589,7 +613,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -612,11 +636,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -636,12 +669,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,12 +993,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1675,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -1684,13 +1720,13 @@
     <col min="5" max="5" width="56.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1707,7 +1743,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="50" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="50" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
@@ -1720,8 +1756,11 @@
       <c r="D4" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="25" x14ac:dyDescent="0.35">
+      <c r="F4" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -1735,7 +1774,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1752,7 +1791,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
@@ -1766,7 +1805,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -1779,11 +1818,11 @@
       <c r="D8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
@@ -1800,7 +1839,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>53</v>
       </c>
@@ -1814,7 +1853,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>60</v>
       </c>
@@ -1828,7 +1867,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -1842,7 +1881,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>71</v>
       </c>
@@ -1856,7 +1895,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>85</v>
       </c>
@@ -1870,7 +1909,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>90</v>
       </c>
@@ -1884,7 +1923,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>96</v>
       </c>
@@ -1932,10 +1971,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
